--- a/Excel/EquipRefineFeeConfig.xlsx
+++ b/Excel/EquipRefineFeeConfig.xlsx
@@ -1132,10 +1132,10 @@
         <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="G6" s="2">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="H6" s="2">
         <v>10</v>
@@ -1160,10 +1160,10 @@
         <v>20</v>
       </c>
       <c r="F7" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="G7" s="2">
         <v>200000</v>
-      </c>
-      <c r="G7" s="2">
-        <v>100000</v>
       </c>
       <c r="H7" s="2">
         <v>120</v>
@@ -1188,10 +1188,10 @@
         <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>2000000</v>
+        <v>3300000</v>
       </c>
       <c r="G8" s="2">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="H8" s="2">
         <v>330</v>
@@ -1216,10 +1216,10 @@
         <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>20000000</v>
+        <v>6400000</v>
       </c>
       <c r="G9" s="2">
-        <v>10000000</v>
+        <v>400000</v>
       </c>
       <c r="H9" s="2">
         <v>640</v>
@@ -1244,10 +1244,10 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>200000000</v>
+        <v>10000000</v>
       </c>
       <c r="G10" s="2">
-        <v>100000000</v>
+        <v>1000000</v>
       </c>
       <c r="H10" s="2">
         <v>1100</v>
@@ -1272,10 +1272,10 @@
         <v>60</v>
       </c>
       <c r="F11" s="2">
-        <v>2000000000</v>
+        <v>20000000</v>
       </c>
       <c r="G11" s="2">
-        <v>1000000000</v>
+        <v>2000000</v>
       </c>
       <c r="H11" s="2">
         <v>2200</v>

--- a/Excel/EquipRefineFeeConfig.xlsx
+++ b/Excel/EquipRefineFeeConfig.xlsx
@@ -1132,16 +1132,16 @@
         <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G6" s="2">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="H6" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
@@ -1160,16 +1160,16 @@
         <v>20</v>
       </c>
       <c r="F7" s="2">
-        <v>1200000</v>
+        <v>120000</v>
       </c>
       <c r="G7" s="2">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="H7" s="2">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I7" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
@@ -1188,16 +1188,16 @@
         <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>3300000</v>
+        <v>330000</v>
       </c>
       <c r="G8" s="2">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="H8" s="2">
-        <v>330</v>
+        <v>33</v>
       </c>
       <c r="I8" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
@@ -1216,16 +1216,16 @@
         <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>6400000</v>
+        <v>640000</v>
       </c>
       <c r="G9" s="2">
-        <v>400000</v>
+        <v>40000</v>
       </c>
       <c r="H9" s="2">
-        <v>640</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
@@ -1244,16 +1244,16 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>10000000</v>
+        <v>1000000</v>
       </c>
       <c r="G10" s="2">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="H10" s="2">
-        <v>1100</v>
+        <v>110</v>
       </c>
       <c r="I10" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
@@ -1272,16 +1272,16 @@
         <v>60</v>
       </c>
       <c r="F11" s="2">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="G11" s="2">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="H11" s="2">
-        <v>2200</v>
+        <v>220</v>
       </c>
       <c r="I11" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>

--- a/Excel/EquipRefineFeeConfig.xlsx
+++ b/Excel/EquipRefineFeeConfig.xlsx
@@ -1160,6 +1160,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="2">
+        <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6+G7</f>
         <v>120000</v>
       </c>
       <c r="G7" s="2">
@@ -1188,10 +1189,11 @@
         <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>330000</v>
+        <f t="shared" si="1"/>
+        <v>340000</v>
       </c>
       <c r="G8" s="2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="H8" s="2">
         <v>33</v>
@@ -1216,10 +1218,11 @@
         <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>640000</v>
+        <f t="shared" si="1"/>
+        <v>770000</v>
       </c>
       <c r="G9" s="2">
-        <v>40000</v>
+        <v>70000</v>
       </c>
       <c r="H9" s="2">
         <v>64</v>
@@ -1244,7 +1247,8 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>1000000</v>
+        <f t="shared" si="1"/>
+        <v>1500000</v>
       </c>
       <c r="G10" s="2">
         <v>100000</v>
@@ -1272,7 +1276,8 @@
         <v>60</v>
       </c>
       <c r="F11" s="2">
-        <v>2000000</v>
+        <f t="shared" si="1"/>
+        <v>2600000</v>
       </c>
       <c r="G11" s="2">
         <v>200000</v>

--- a/Excel/EquipRefineFeeConfig.xlsx
+++ b/Excel/EquipRefineFeeConfig.xlsx
@@ -1161,10 +1161,10 @@
       </c>
       <c r="F7" s="2">
         <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6+G7</f>
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="G7" s="2">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="H7" s="2">
         <v>12</v>
@@ -1190,10 +1190,10 @@
       </c>
       <c r="F8" s="2">
         <f t="shared" si="1"/>
-        <v>340000</v>
+        <v>900000</v>
       </c>
       <c r="G8" s="2">
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="H8" s="2">
         <v>33</v>
@@ -1219,10 +1219,10 @@
       </c>
       <c r="F9" s="2">
         <f t="shared" si="1"/>
-        <v>770000</v>
+        <v>5600000</v>
       </c>
       <c r="G9" s="2">
-        <v>70000</v>
+        <v>2000000</v>
       </c>
       <c r="H9" s="2">
         <v>64</v>
@@ -1248,10 +1248,10 @@
       </c>
       <c r="F10" s="2">
         <f t="shared" si="1"/>
-        <v>1500000</v>
+        <v>33600000</v>
       </c>
       <c r="G10" s="2">
-        <v>100000</v>
+        <v>10000000</v>
       </c>
       <c r="H10" s="2">
         <v>110</v>
@@ -1277,10 +1277,10 @@
       </c>
       <c r="F11" s="2">
         <f t="shared" si="1"/>
-        <v>2600000</v>
+        <v>173600000</v>
       </c>
       <c r="G11" s="2">
-        <v>200000</v>
+        <v>50000000</v>
       </c>
       <c r="H11" s="2">
         <v>220</v>

--- a/Excel/EquipRefineFeeConfig.xlsx
+++ b/Excel/EquipRefineFeeConfig.xlsx
@@ -1161,10 +1161,10 @@
       </c>
       <c r="F7" s="2">
         <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6+G7</f>
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="G7" s="2">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="H7" s="2">
         <v>12</v>
@@ -1190,10 +1190,10 @@
       </c>
       <c r="F8" s="2">
         <f t="shared" si="1"/>
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="G8" s="2">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="H8" s="2">
         <v>33</v>
@@ -1219,16 +1219,16 @@
       </c>
       <c r="F9" s="2">
         <f t="shared" si="1"/>
-        <v>5600000</v>
+        <v>3500000</v>
       </c>
       <c r="G9" s="2">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="H9" s="2">
         <v>64</v>
       </c>
       <c r="I9" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
@@ -1248,16 +1248,16 @@
       </c>
       <c r="F10" s="2">
         <f t="shared" si="1"/>
-        <v>33600000</v>
+        <v>16500000</v>
       </c>
       <c r="G10" s="2">
-        <v>10000000</v>
+        <v>4000000</v>
       </c>
       <c r="H10" s="2">
         <v>110</v>
       </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
@@ -1277,16 +1277,16 @@
       </c>
       <c r="F11" s="2">
         <f t="shared" si="1"/>
-        <v>173600000</v>
+        <v>72500000</v>
       </c>
       <c r="G11" s="2">
-        <v>50000000</v>
+        <v>20000000</v>
       </c>
       <c r="H11" s="2">
         <v>220</v>
       </c>
       <c r="I11" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>

--- a/Excel/EquipRefineFeeConfig.xlsx
+++ b/Excel/EquipRefineFeeConfig.xlsx
@@ -1161,10 +1161,10 @@
       </c>
       <c r="F7" s="2">
         <f t="shared" ref="F7:F11" si="1">F6+(E6-D6)*G6+G7</f>
-        <v>140000</v>
+        <v>130000</v>
       </c>
       <c r="G7" s="2">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="H7" s="2">
         <v>12</v>
@@ -1190,10 +1190,10 @@
       </c>
       <c r="F8" s="2">
         <f t="shared" si="1"/>
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="G8" s="2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="H8" s="2">
         <v>33</v>
@@ -1219,10 +1219,10 @@
       </c>
       <c r="F9" s="2">
         <f t="shared" si="1"/>
-        <v>3500000</v>
+        <v>1700000</v>
       </c>
       <c r="G9" s="2">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="2">
         <v>64</v>
@@ -1248,10 +1248,10 @@
       </c>
       <c r="F10" s="2">
         <f t="shared" si="1"/>
-        <v>16500000</v>
+        <v>5400000</v>
       </c>
       <c r="G10" s="2">
-        <v>4000000</v>
+        <v>1000000</v>
       </c>
       <c r="H10" s="2">
         <v>110</v>
@@ -1277,10 +1277,10 @@
       </c>
       <c r="F11" s="2">
         <f t="shared" si="1"/>
-        <v>72500000</v>
+        <v>17400000</v>
       </c>
       <c r="G11" s="2">
-        <v>20000000</v>
+        <v>3000000</v>
       </c>
       <c r="H11" s="2">
         <v>220</v>
